--- a/lwc-feature-tables/LanguageWorkbench_FeatureConfiguration.xlsx
+++ b/lwc-feature-tables/LanguageWorkbench_FeatureConfiguration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tgiraudet\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeff/Git/PL/metaborg-ql/lwc-feature-tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAAF3E9-8E5C-4999-A5BE-3E0F27BB1FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E7207A-3822-E04B-90E3-E633BAC19267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FD4AA70-ECA5-4D89-879B-07B2E8F8F0C4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="28300" xr2:uid="{7FD4AA70-ECA5-4D89-879B-07B2E8F8F0C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="182">
   <si>
     <t>Language Workbench</t>
   </si>
@@ -43,9 +43,6 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>&lt;Language workbench name&gt;</t>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
@@ -494,6 +491,96 @@
   </si>
   <si>
     <t>│   └── Versioning</t>
+  </si>
+  <si>
+    <t>Spoofax</t>
+  </si>
+  <si>
+    <t>Either derived from the SDF3 specification of the concrete syntax, or manually written in Stratego algebraic signatures</t>
+  </si>
+  <si>
+    <t>With the SDF3 meta-language</t>
+  </si>
+  <si>
+    <t>Default behaviour with SDF3</t>
+  </si>
+  <si>
+    <t>Through desugaring in Stratego</t>
+  </si>
+  <si>
+    <t>Through Stratego's string template</t>
+  </si>
+  <si>
+    <t>Through Stratego term rewriting</t>
+  </si>
+  <si>
+    <t>Through Stratego's support for mix syntax</t>
+  </si>
+  <si>
+    <t>Through Stratego</t>
+  </si>
+  <si>
+    <t>limited support</t>
+  </si>
+  <si>
+    <t>Through Stratego, by using similar conventions in interpreter/translation</t>
+  </si>
+  <si>
+    <t>Using the Statix meta-language</t>
+  </si>
+  <si>
+    <t>Depends on your definition, supported in Statix and Stratego</t>
+  </si>
+  <si>
+    <t>With Statix</t>
+  </si>
+  <si>
+    <t>With Stratego</t>
+  </si>
+  <si>
+    <t>Automatically derived from SDF3 spec</t>
+  </si>
+  <si>
+    <t>Defined in ESV meta-language</t>
+  </si>
+  <si>
+    <t>Automatically derived from Statix spec</t>
+  </si>
+  <si>
+    <t>Stratego supports gradual types that can do runtime checking of structure</t>
+  </si>
+  <si>
+    <t>Through Statix</t>
+  </si>
+  <si>
+    <t>Not for all meta-languages yet</t>
+  </si>
+  <si>
+    <t>Side-effects are possible in Stratego</t>
+  </si>
+  <si>
+    <t>Through the SPT meta-language</t>
+  </si>
+  <si>
+    <t>Through SDF3 grammar composition</t>
+  </si>
+  <si>
+    <t>Limited to those derived from SDF3</t>
+  </si>
+  <si>
+    <t>Requires definition of hooks in the base language for modification by an extension</t>
+  </si>
+  <si>
+    <t>Through text-based VCS</t>
+  </si>
+  <si>
+    <t>Modular architecture of services based on Java APIs</t>
+  </si>
+  <si>
+    <t>Hot-reloading the language/editor/interpreter/etc.</t>
+  </si>
+  <si>
+    <t>SDF3 has deprecation annotations</t>
   </si>
 </sst>
 </file>
@@ -522,15 +609,21 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -600,11 +693,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFF4B084"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF4B084"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF4B084"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFF4B084"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF4B084"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -618,14 +735,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -641,6 +757,9 @@
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -655,11 +774,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{386018CC-2DD9-414B-A04F-9CCD124002F8}" name="Tableau2" displayName="Tableau2" ref="A1:C145" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{386018CC-2DD9-414B-A04F-9CCD124002F8}" name="Tableau2" displayName="Tableau2" ref="A1:C145" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:C145" xr:uid="{386018CC-2DD9-414B-A04F-9CCD124002F8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B406174F-A27E-4E0E-91B4-F2C68E845F5A}" name="Feature" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{30F54B26-B672-4A8D-BBBF-87E3312A1E8C}" name="&lt;Language workbench name&gt;"/>
+    <tableColumn id="1" xr3:uid="{B406174F-A27E-4E0E-91B4-F2C68E845F5A}" name="Feature" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{30F54B26-B672-4A8D-BBBF-87E3312A1E8C}" name="Spoofax"/>
     <tableColumn id="3" xr3:uid="{DE361FCB-B5CF-4524-8295-676BC12229C6}" name="Comments"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -667,9 +786,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -707,7 +826,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -813,7 +932,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -955,7 +1074,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -964,1042 +1083,1445 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0467C85-CDFA-45E8-AEAF-B61FBEF68F92}">
   <dimension ref="A1:F145"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="54.453125" customWidth="1"/>
-    <col min="2" max="2" width="31.453125" customWidth="1"/>
+    <col min="1" max="1" width="54.5" customWidth="1"/>
+    <col min="2" max="2" width="31.5" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="47.36328125" customWidth="1"/>
+    <col min="6" max="6" width="47.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>15</v>
+      <c r="B8" t="s">
+        <v>6</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="F10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="B30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="B31" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="B33" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="8" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="B36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="8" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+      <c r="B40" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="B41" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="8" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="B46" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
+      <c r="B49" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
+      <c r="B50" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="B51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="8" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
+      <c r="B58" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="8" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
+      <c r="B61" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="B62" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="8" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="8" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
+      <c r="B66" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="8" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="8" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="8" t="s">
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="8" t="s">
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="8" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
+      <c r="B72" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="8" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="8" t="s">
+      <c r="B73" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="8" t="s">
+      <c r="B74" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="8" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="8" t="s">
+      <c r="B75" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="8" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="8" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="8" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="8" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="8" t="s">
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="8" t="s">
+      <c r="B81" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B81" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="8" t="s">
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="8" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="8" t="s">
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="8" t="s">
+      <c r="B84" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="8" t="s">
+      <c r="B85" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="8" t="s">
+      <c r="B86" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="8" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" s="8" t="s">
+      <c r="B87" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="8" t="s">
+      <c r="B88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="8" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" s="8" t="s">
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="8" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="8" t="s">
+      <c r="B90" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="8" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="8" t="s">
+      <c r="B91" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="8" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="8" t="s">
+      <c r="B92" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="8" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="8" t="s">
+      <c r="B93" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B93" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" s="8" t="s">
+      <c r="B94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B94" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="8" t="s">
+      <c r="B95" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" s="8" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" s="8" t="s">
+      <c r="B96" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="8" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="8" t="s">
+      <c r="B97" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="8" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="8" t="s">
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="8" t="s">
+      <c r="B99" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B99" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="8" t="s">
+      <c r="B100" t="s">
+        <v>161</v>
+      </c>
+      <c r="C100" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="8" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="8" t="s">
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="8" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="8" t="s">
+      <c r="B102" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B102" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="8" t="s">
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" s="8" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" s="8" t="s">
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" s="8" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="8" t="s">
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="8" t="s">
+      <c r="B106" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B106" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" s="8" t="s">
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" s="8" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" s="8" t="s">
+      <c r="B108" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" s="8" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" s="8" t="s">
+      <c r="B109" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" s="8" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" s="8" t="s">
+      <c r="B110" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B110" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" s="8" t="s">
+      <c r="B111" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B111" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" s="8" t="s">
+      <c r="B112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" s="8" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" s="8" t="s">
+      <c r="B113" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" s="8" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" s="8" t="s">
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" s="8" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="8" t="s">
+      <c r="B115" t="s">
+        <v>161</v>
+      </c>
+      <c r="C115" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" s="8" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" s="8" t="s">
+      <c r="B116" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B116" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="8" t="s">
+      <c r="B117" t="s">
+        <v>161</v>
+      </c>
+      <c r="C117" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" s="8" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" s="8" t="s">
+      <c r="B118" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119" s="8" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="8" t="s">
+      <c r="B119" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" s="8" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" s="8" t="s">
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" s="8" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" s="8" t="s">
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122" s="8" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" s="8" t="s">
+      <c r="B122" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B122" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="8" t="s">
+      <c r="B123" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B123" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" s="8" t="s">
+      <c r="B124" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B124" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" s="8" t="s">
+      <c r="B125" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126" s="8" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" s="8" t="s">
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127" s="8" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" s="8" t="s">
+      <c r="B127" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B127" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128" s="8" t="s">
+      <c r="B128" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A129" s="8" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" s="8" t="s">
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A130" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B130" t="s">
+        <v>161</v>
+      </c>
+      <c r="C130" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131" s="8" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131" s="8" t="s">
+      <c r="B131" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A132" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B131" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132" s="8" t="s">
+      <c r="B132" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A133" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B132" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" s="8" t="s">
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A134" s="8" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134" s="8" t="s">
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A135" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A136" s="8" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135" s="8" t="s">
+      <c r="B136" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A137" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A138" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A139" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A140" s="8" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" s="8" t="s">
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A141" s="8" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" s="8" t="s">
+      <c r="B141" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A142" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B141" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" s="8" t="s">
+      <c r="B142" t="s">
+        <v>161</v>
+      </c>
+      <c r="C142" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A143" s="8" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143" s="8" t="s">
+      <c r="B143" t="s">
+        <v>161</v>
+      </c>
+      <c r="C143" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144" s="8" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" s="8" t="s">
+      <c r="B144" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A145" s="8" t="s">
-        <v>149</v>
+      <c r="B145" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
